--- a/artfynd/A 31363-2024 artfynd.xlsx
+++ b/artfynd/A 31363-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118883831</v>
+        <v>118883837</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564766</v>
+        <v>564795</v>
       </c>
       <c r="R2" t="n">
-        <v>6688402</v>
+        <v>6688410</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118883818</v>
+        <v>118883863</v>
       </c>
       <c r="B3" t="n">
-        <v>57443</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,43 +798,54 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564796</v>
+        <v>564527</v>
       </c>
       <c r="R3" t="n">
-        <v>6688411</v>
+        <v>6688795</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,12 +880,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,7 +910,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118883837</v>
+        <v>118883831</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -928,7 +945,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -942,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564795</v>
+        <v>564766</v>
       </c>
       <c r="R4" t="n">
-        <v>6688410</v>
+        <v>6688402</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1004,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118883863</v>
+        <v>118883818</v>
       </c>
       <c r="B5" t="n">
-        <v>97853</v>
+        <v>57443</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,54 +1033,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564527</v>
+        <v>564796</v>
       </c>
       <c r="R5" t="n">
-        <v>6688795</v>
+        <v>6688411</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,18 +1104,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118883835</v>
+        <v>118883853</v>
       </c>
       <c r="B39" t="n">
         <v>97853</v>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564528</v>
+        <v>564759</v>
       </c>
       <c r="R39" t="n">
-        <v>6688801</v>
+        <v>6688391</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5044,7 +5044,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118883820</v>
+        <v>118883842</v>
       </c>
       <c r="B40" t="n">
         <v>97853</v>
@@ -5078,23 +5078,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>564746</v>
+        <v>564529</v>
       </c>
       <c r="R40" t="n">
-        <v>6688406</v>
+        <v>6688802</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5129,18 +5122,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5159,7 +5146,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118883853</v>
+        <v>118883835</v>
       </c>
       <c r="B41" t="n">
         <v>97853</v>
@@ -5194,7 +5181,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5208,10 +5195,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>564759</v>
+        <v>564528</v>
       </c>
       <c r="R41" t="n">
-        <v>6688391</v>
+        <v>6688801</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5270,7 +5257,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118883842</v>
+        <v>118883820</v>
       </c>
       <c r="B42" t="n">
         <v>97853</v>
@@ -5304,16 +5291,23 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564529</v>
+        <v>564746</v>
       </c>
       <c r="R42" t="n">
-        <v>6688802</v>
+        <v>6688406</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5348,12 +5342,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31363-2024 artfynd.xlsx
+++ b/artfynd/A 31363-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118883837</v>
+        <v>118883839</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564795</v>
+        <v>564764</v>
       </c>
       <c r="R2" t="n">
-        <v>6688410</v>
+        <v>6688416</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118883863</v>
+        <v>118883847</v>
       </c>
       <c r="B3" t="n">
         <v>97853</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -829,23 +829,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564527</v>
+        <v>564744</v>
       </c>
       <c r="R3" t="n">
-        <v>6688795</v>
+        <v>6688400</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -880,18 +873,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118883831</v>
+        <v>118883834</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -945,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -953,16 +940,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564766</v>
+        <v>564764</v>
       </c>
       <c r="R4" t="n">
-        <v>6688402</v>
+        <v>6688384</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -997,12 +991,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118883818</v>
+        <v>118883838</v>
       </c>
       <c r="B5" t="n">
-        <v>57443</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,31 +1033,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564796</v>
+        <v>564789</v>
       </c>
       <c r="R5" t="n">
-        <v>6688411</v>
+        <v>6688410</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1128,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118883845</v>
+        <v>118883853</v>
       </c>
       <c r="B6" t="n">
         <v>97853</v>
@@ -1163,7 +1167,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1171,23 +1175,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564765</v>
+        <v>564759</v>
       </c>
       <c r="R6" t="n">
-        <v>6688393</v>
+        <v>6688391</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1222,18 +1219,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1252,7 +1243,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118883822</v>
+        <v>118883849</v>
       </c>
       <c r="B7" t="n">
         <v>97853</v>
@@ -1285,24 +1276,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564758</v>
+        <v>564804</v>
       </c>
       <c r="R7" t="n">
-        <v>6688398</v>
+        <v>6688414</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1337,18 +1330,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1367,7 +1354,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118883856</v>
+        <v>118883862</v>
       </c>
       <c r="B8" t="n">
         <v>97853</v>
@@ -1402,7 +1389,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1410,23 +1397,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564811</v>
+        <v>564743</v>
       </c>
       <c r="R8" t="n">
-        <v>6688391</v>
+        <v>6688427</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1461,18 +1441,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>4 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1491,7 +1465,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118883861</v>
+        <v>118883856</v>
       </c>
       <c r="B9" t="n">
         <v>97853</v>
@@ -1526,7 +1500,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1534,16 +1508,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564735</v>
+        <v>564811</v>
       </c>
       <c r="R9" t="n">
-        <v>6688435</v>
+        <v>6688391</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1578,12 +1559,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>4 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1602,7 +1589,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118883855</v>
+        <v>118883845</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1637,7 +1624,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1645,16 +1632,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564773</v>
+        <v>564765</v>
       </c>
       <c r="R10" t="n">
-        <v>6688371</v>
+        <v>6688393</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1689,12 +1683,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1713,7 +1713,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118883847</v>
+        <v>118883831</v>
       </c>
       <c r="B11" t="n">
         <v>97853</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564744</v>
+        <v>564766</v>
       </c>
       <c r="R11" t="n">
-        <v>6688400</v>
+        <v>6688402</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118883851</v>
+        <v>118883837</v>
       </c>
       <c r="B12" t="n">
         <v>97853</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564752</v>
+        <v>564795</v>
       </c>
       <c r="R12" t="n">
-        <v>6688399</v>
+        <v>6688410</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1935,7 +1935,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118883859</v>
+        <v>118883826</v>
       </c>
       <c r="B13" t="n">
         <v>97853</v>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1978,16 +1978,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564744</v>
+        <v>564765</v>
       </c>
       <c r="R13" t="n">
-        <v>6688406</v>
+        <v>6688387</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2022,12 +2029,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2046,7 +2059,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118883844</v>
+        <v>118883835</v>
       </c>
       <c r="B14" t="n">
         <v>97853</v>
@@ -2081,7 +2094,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2089,23 +2102,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564791</v>
+        <v>564528</v>
       </c>
       <c r="R14" t="n">
-        <v>6688384</v>
+        <v>6688801</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2140,18 +2146,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118883846</v>
+        <v>118883859</v>
       </c>
       <c r="B15" t="n">
         <v>97853</v>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564737</v>
+        <v>564744</v>
       </c>
       <c r="R15" t="n">
-        <v>6688416</v>
+        <v>6688406</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2281,7 +2281,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118883826</v>
+        <v>118883829</v>
       </c>
       <c r="B16" t="n">
         <v>97853</v>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2324,23 +2324,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564765</v>
+        <v>564739</v>
       </c>
       <c r="R16" t="n">
-        <v>6688387</v>
+        <v>6688411</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2375,18 +2368,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2405,7 +2392,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118883836</v>
+        <v>118883857</v>
       </c>
       <c r="B17" t="n">
         <v>97853</v>
@@ -2440,7 +2427,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2448,16 +2435,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564745</v>
+        <v>564800</v>
       </c>
       <c r="R17" t="n">
-        <v>6688379</v>
+        <v>6688384</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2492,12 +2486,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118883839</v>
+        <v>118883825</v>
       </c>
       <c r="B18" t="n">
         <v>97853</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2559,6 +2559,13 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
@@ -2568,7 +2575,7 @@
         <v>564764</v>
       </c>
       <c r="R18" t="n">
-        <v>6688416</v>
+        <v>6688366</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2603,12 +2610,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2627,7 +2640,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118883840</v>
+        <v>118883822</v>
       </c>
       <c r="B19" t="n">
         <v>97853</v>
@@ -2660,26 +2673,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564741</v>
+        <v>564758</v>
       </c>
       <c r="R19" t="n">
-        <v>6688423</v>
+        <v>6688398</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2714,12 +2725,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2738,7 +2755,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118883834</v>
+        <v>118883850</v>
       </c>
       <c r="B20" t="n">
         <v>97853</v>
@@ -2773,7 +2790,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2781,23 +2798,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564764</v>
+        <v>564773</v>
       </c>
       <c r="R20" t="n">
-        <v>6688384</v>
+        <v>6688408</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2832,18 +2842,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2862,7 +2866,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118883830</v>
+        <v>118883863</v>
       </c>
       <c r="B21" t="n">
         <v>97853</v>
@@ -2897,7 +2901,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2905,16 +2909,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564781</v>
+        <v>564527</v>
       </c>
       <c r="R21" t="n">
-        <v>6688406</v>
+        <v>6688795</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2949,12 +2960,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2973,7 +2990,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118883838</v>
+        <v>118883830</v>
       </c>
       <c r="B22" t="n">
         <v>97853</v>
@@ -3008,7 +3025,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3022,10 +3039,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564789</v>
+        <v>564781</v>
       </c>
       <c r="R22" t="n">
-        <v>6688410</v>
+        <v>6688406</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3084,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118883848</v>
+        <v>118883817</v>
       </c>
       <c r="B23" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3096,47 +3113,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564743</v>
+        <v>564628</v>
       </c>
       <c r="R23" t="n">
-        <v>6688403</v>
+        <v>6688683</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3195,7 +3203,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118883857</v>
+        <v>118883846</v>
       </c>
       <c r="B24" t="n">
         <v>97853</v>
@@ -3230,7 +3238,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3238,23 +3246,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564800</v>
+        <v>564737</v>
       </c>
       <c r="R24" t="n">
-        <v>6688384</v>
+        <v>6688416</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3289,18 +3290,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3319,10 +3314,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118883817</v>
+        <v>118883840</v>
       </c>
       <c r="B25" t="n">
-        <v>90511</v>
+        <v>97853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3331,38 +3326,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564628</v>
+        <v>564741</v>
       </c>
       <c r="R25" t="n">
-        <v>6688683</v>
+        <v>6688423</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3421,7 +3425,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118883832</v>
+        <v>118883827</v>
       </c>
       <c r="B26" t="n">
         <v>97853</v>
@@ -3456,7 +3460,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3470,10 +3474,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564755</v>
+        <v>564764</v>
       </c>
       <c r="R26" t="n">
-        <v>6688357</v>
+        <v>6688365</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3532,10 +3536,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118883833</v>
+        <v>118883818</v>
       </c>
       <c r="B27" t="n">
-        <v>97853</v>
+        <v>57443</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3544,51 +3548,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564792</v>
+        <v>564796</v>
       </c>
       <c r="R27" t="n">
         <v>6688411</v>
@@ -3626,18 +3619,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3656,7 +3643,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118883858</v>
+        <v>118883844</v>
       </c>
       <c r="B28" t="n">
         <v>97853</v>
@@ -3691,7 +3678,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3712,10 +3699,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564766</v>
+        <v>564791</v>
       </c>
       <c r="R28" t="n">
-        <v>6688397</v>
+        <v>6688384</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3752,7 +3739,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3780,7 +3767,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118883850</v>
+        <v>118883855</v>
       </c>
       <c r="B29" t="n">
         <v>97853</v>
@@ -3815,7 +3802,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3832,7 +3819,7 @@
         <v>564773</v>
       </c>
       <c r="R29" t="n">
-        <v>6688408</v>
+        <v>6688371</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3891,7 +3878,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118883825</v>
+        <v>118883848</v>
       </c>
       <c r="B30" t="n">
         <v>97853</v>
@@ -3926,7 +3913,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3934,23 +3921,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>564764</v>
+        <v>564743</v>
       </c>
       <c r="R30" t="n">
-        <v>6688366</v>
+        <v>6688403</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3985,18 +3965,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4015,7 +3989,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118883829</v>
+        <v>118883842</v>
       </c>
       <c r="B31" t="n">
         <v>97853</v>
@@ -4048,26 +4022,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564739</v>
+        <v>564529</v>
       </c>
       <c r="R31" t="n">
-        <v>6688411</v>
+        <v>6688802</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4126,7 +4091,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118883823</v>
+        <v>118883836</v>
       </c>
       <c r="B32" t="n">
         <v>97853</v>
@@ -4161,7 +4126,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4169,23 +4134,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564766</v>
+        <v>564745</v>
       </c>
       <c r="R32" t="n">
-        <v>6688369</v>
+        <v>6688379</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4220,18 +4178,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4250,7 +4202,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118883849</v>
+        <v>118883823</v>
       </c>
       <c r="B33" t="n">
         <v>97853</v>
@@ -4285,7 +4237,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4293,16 +4245,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>564804</v>
+        <v>564766</v>
       </c>
       <c r="R33" t="n">
-        <v>6688414</v>
+        <v>6688369</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4337,12 +4296,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4361,7 +4326,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118883862</v>
+        <v>118883833</v>
       </c>
       <c r="B34" t="n">
         <v>97853</v>
@@ -4396,7 +4361,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4404,16 +4369,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>564743</v>
+        <v>564792</v>
       </c>
       <c r="R34" t="n">
-        <v>6688427</v>
+        <v>6688411</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4448,12 +4420,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4472,7 +4450,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118883860</v>
+        <v>118883854</v>
       </c>
       <c r="B35" t="n">
         <v>97853</v>
@@ -4507,7 +4485,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4515,16 +4493,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>564785</v>
+        <v>564750</v>
       </c>
       <c r="R35" t="n">
-        <v>6688407</v>
+        <v>6688376</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4559,12 +4544,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4583,7 +4574,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118883827</v>
+        <v>118883832</v>
       </c>
       <c r="B36" t="n">
         <v>97853</v>
@@ -4618,7 +4609,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4632,10 +4623,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564764</v>
+        <v>564755</v>
       </c>
       <c r="R36" t="n">
-        <v>6688365</v>
+        <v>6688357</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4694,7 +4685,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118883821</v>
+        <v>118883861</v>
       </c>
       <c r="B37" t="n">
         <v>97853</v>
@@ -4727,24 +4718,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>564805</v>
+        <v>564735</v>
       </c>
       <c r="R37" t="n">
-        <v>6688386</v>
+        <v>6688435</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4779,18 +4772,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4809,7 +4796,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118883854</v>
+        <v>118883860</v>
       </c>
       <c r="B38" t="n">
         <v>97853</v>
@@ -4844,7 +4831,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4852,23 +4839,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>564750</v>
+        <v>564785</v>
       </c>
       <c r="R38" t="n">
-        <v>6688376</v>
+        <v>6688407</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4903,18 +4883,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4933,7 +4907,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118883853</v>
+        <v>118883820</v>
       </c>
       <c r="B39" t="n">
         <v>97853</v>
@@ -4966,26 +4940,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564759</v>
+        <v>564746</v>
       </c>
       <c r="R39" t="n">
-        <v>6688391</v>
+        <v>6688406</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5020,12 +4992,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5044,7 +5022,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118883842</v>
+        <v>118883858</v>
       </c>
       <c r="B40" t="n">
         <v>97853</v>
@@ -5077,17 +5055,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>564529</v>
+        <v>564766</v>
       </c>
       <c r="R40" t="n">
-        <v>6688802</v>
+        <v>6688397</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5122,12 +5116,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5146,7 +5146,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118883835</v>
+        <v>118883821</v>
       </c>
       <c r="B41" t="n">
         <v>97853</v>
@@ -5179,26 +5179,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>564528</v>
+        <v>564805</v>
       </c>
       <c r="R41" t="n">
-        <v>6688801</v>
+        <v>6688386</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5233,12 +5231,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5257,7 +5261,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118883820</v>
+        <v>118883851</v>
       </c>
       <c r="B42" t="n">
         <v>97853</v>
@@ -5290,24 +5294,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lissjön, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564746</v>
+        <v>564752</v>
       </c>
       <c r="R42" t="n">
-        <v>6688406</v>
+        <v>6688399</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5342,18 +5348,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
